--- a/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
+++ b/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Green Grape / Muscat Grape</t>
+          <t>Muscat Grape</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">

--- a/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
+++ b/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Spicy Grilled Cheese Curry</t>
+          <t>Extra Spicy Grilled Cheese Curry</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>過去限定。定番と同名になるため差別化が必要</t>
+          <t>過去限定。海外店の Spicy Grilled Cheese Curry と区別するため Extra Spicy を付けた（2026年9月15日 決定）</t>
         </is>
       </c>
     </row>

--- a/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
+++ b/docs/rename-2026-10/out/商品名リネーム（2026年10月 全店改変）.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>日本固有の味のため和名維持。説明文必須</t>
+          <t>日本固有の味のため和名維持。説明文必須。海外は Anko &amp; Butter（北海道産に限定できないため Hokkaido を外す）</t>
         </is>
       </c>
     </row>
